--- a/assets/template/old_payment_history.xlsx
+++ b/assets/template/old_payment_history.xlsx
@@ -1,40 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="29">
   <si>
     <t xml:space="preserve">Coustomer ID</t>
   </si>
   <si>
-    <t xml:space="preserve">26LA000001</t>
+    <t xml:space="preserve">26LA000083</t>
   </si>
   <si>
     <t xml:space="preserve">Account No.</t>
   </si>
   <si>
-    <t xml:space="preserve">MF2026A000001</t>
+    <t xml:space="preserve">MF26A000083</t>
   </si>
   <si>
     <t xml:space="preserve">Loanee Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Ramesh Kumar</t>
+    <t xml:space="preserve">Naosekpam Malabati</t>
   </si>
   <si>
     <t xml:space="preserve">Route</t>
   </si>
   <si>
-    <t xml:space="preserve">Angom</t>
+    <t xml:space="preserve">Moirang</t>
   </si>
   <si>
     <t xml:space="preserve">Collection Types</t>
@@ -46,7 +55,7 @@
     <t xml:space="preserve">Collected By</t>
   </si>
   <si>
-    <t xml:space="preserve">Dev</t>
+    <t xml:space="preserve">Office Entry</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -55,52 +64,164 @@
     <t xml:space="preserve">Payment Amount</t>
   </si>
   <si>
-    <t xml:space="preserve">Interest</t>
+    <t xml:space="preserve">Late Payment Interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post Maturity Interest</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 29.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 120.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ -   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 3.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 180.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 100.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 250.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 50.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 60.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 1.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 150.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 130.00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ₹ 577.00 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="167" formatCode="mm/dd/yy"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
-    <font/>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="14" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="2" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -146,59 +267,55 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -206,33 +323,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -245,13 +353,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -261,15 +363,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -277,7 +377,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -285,11 +384,11 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -298,13 +397,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <sheetFormatPr defaultRowHeight="15.75" defaultColWidth="14.43"/>
+  <dimension ref="A1:D127"/>
+  <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -312,7 +413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -320,7 +421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -328,7 +429,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -336,7 +437,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -344,7 +445,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -352,7 +453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -362,63 +463,1174 @@
       <c r="C7" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>46204.0</v>
-      </c>
-      <c r="B8" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>150.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>46205.0</v>
-      </c>
-      <c r="B9" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>46206.0</v>
-      </c>
-      <c r="B10" s="3">
-        <v>300.0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>46207.0</v>
-      </c>
-      <c r="B11" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>45.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>46208.0</v>
-      </c>
-      <c r="B12" s="3">
-        <v>200.0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>56.0</v>
+      <c r="D7" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="4" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="4" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="4" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="4" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="4" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="4" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B35" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="4" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B36" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="4" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B37" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="4" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B38" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="4" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B39" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="4" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B40" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="4" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B41" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="4" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="4" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B45" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="4" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B46" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B47" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="4" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B48" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B49" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B50" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="4" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B51" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B52" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="4" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B53" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="4" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B55" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="4" t="n">
+        <v>46186</v>
+      </c>
+      <c r="B56" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="4" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B57" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B58" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B59" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="4" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B60" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="n">
+        <v>46192</v>
+      </c>
+      <c r="B61" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="n">
+        <v>46193</v>
+      </c>
+      <c r="B62" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B63" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B64" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B65" s="0" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B66" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B67" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B68" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B69" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B70" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B71" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="4" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B72" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="4" t="n">
+        <v>46206</v>
+      </c>
+      <c r="B73" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="4" t="n">
+        <v>46207</v>
+      </c>
+      <c r="B74" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B75" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B76" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B77" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B78" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="4" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B79" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C79" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="4" t="n">
+        <v>46214</v>
+      </c>
+      <c r="B80" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="4" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B81" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="4" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B82" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="4" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B83" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C83" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="4" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B84" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C84" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="4" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B85" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="4" t="n">
+        <v>46221</v>
+      </c>
+      <c r="B86" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B87" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B88" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="4" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C90" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="4" t="n">
+        <v>46228</v>
+      </c>
+      <c r="B92" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B95" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B96" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B97" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B98" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B99" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B100" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B101" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C101" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B102" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B103" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C103" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="n">
+        <v>46242</v>
+      </c>
+      <c r="B104" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B105" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B106" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C106" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B107" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C107" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B108" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B109" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B110" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B111" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C111" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B112" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="n">
+        <v>46256</v>
+      </c>
+      <c r="B113" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B114" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="D114" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B115" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C115" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B116" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C116" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B117" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="4" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B118" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="4" t="n">
+        <v>46263</v>
+      </c>
+      <c r="B119" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="4" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B120" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="4" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B121" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="4" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B122" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C122" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="4" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B123" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B124" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C124" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="4" t="n">
+        <v>46272</v>
+      </c>
+      <c r="B125" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C125" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="4" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B126" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C126" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="4" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B127" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C127" s="0" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>